--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/33.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/33.xlsx
@@ -426,13 +426,13 @@
         <v>-22.8102893711675</v>
       </c>
       <c r="E2">
-        <v>-13.41664868197211</v>
+        <v>-16.685147083597</v>
       </c>
       <c r="F2">
-        <v>2.474567712889608</v>
+        <v>1.80750829443725</v>
       </c>
       <c r="G2">
-        <v>-18.14121512748503</v>
+        <v>-19.6139452889381</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-22.58653904096209</v>
       </c>
       <c r="E3">
-        <v>-13.24917874172105</v>
+        <v>-17.21728143780199</v>
       </c>
       <c r="F3">
-        <v>2.392297575913172</v>
+        <v>1.82999349921884</v>
       </c>
       <c r="G3">
-        <v>-16.96007119717962</v>
+        <v>-18.47848547286029</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-22.03235608712818</v>
       </c>
       <c r="E4">
-        <v>-15.94162673259222</v>
+        <v>-17.72153113117207</v>
       </c>
       <c r="F4">
-        <v>2.626859746424686</v>
+        <v>1.891764856445599</v>
       </c>
       <c r="G4">
-        <v>-15.91880443520459</v>
+        <v>-18.15627520765887</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-21.1668532648126</v>
       </c>
       <c r="E5">
-        <v>-15.313083883904</v>
+        <v>-17.67425512666155</v>
       </c>
       <c r="F5">
-        <v>1.940537472387628</v>
+        <v>2.554153939480973</v>
       </c>
       <c r="G5">
-        <v>-15.64856365183386</v>
+        <v>-18.11127641388644</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-20.00540294637563</v>
       </c>
       <c r="E6">
-        <v>-16.73662198475693</v>
+        <v>-18.32257972088993</v>
       </c>
       <c r="F6">
-        <v>2.499668901929238</v>
+        <v>2.052019157456386</v>
       </c>
       <c r="G6">
-        <v>-16.89163966532966</v>
+        <v>-17.53245606282448</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-18.61129502821662</v>
       </c>
       <c r="E7">
-        <v>-15.05112423280176</v>
+        <v>-18.93606717852565</v>
       </c>
       <c r="F7">
-        <v>2.088672758295458</v>
+        <v>2.129062296121156</v>
       </c>
       <c r="G7">
-        <v>-15.94182728638133</v>
+        <v>-17.073536767854</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-17.04480021520308</v>
       </c>
       <c r="E8">
-        <v>-17.49275148534389</v>
+        <v>-18.81019164969275</v>
       </c>
       <c r="F8">
-        <v>2.639530454217907</v>
+        <v>1.822959003234266</v>
       </c>
       <c r="G8">
-        <v>-14.56479918940469</v>
+        <v>-17.03361065082211</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-15.37201995246413</v>
       </c>
       <c r="E9">
-        <v>-17.32333784219281</v>
+        <v>-20.40821446472438</v>
       </c>
       <c r="F9">
-        <v>2.476943470600837</v>
+        <v>2.201208126700577</v>
       </c>
       <c r="G9">
-        <v>-15.00407524207164</v>
+        <v>-16.08606700892345</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.66516456627242</v>
       </c>
       <c r="E10">
-        <v>-18.96611150924946</v>
+        <v>-20.28945338689091</v>
       </c>
       <c r="F10">
-        <v>3.409739838401665</v>
+        <v>2.619010136915758</v>
       </c>
       <c r="G10">
-        <v>-14.15330145918719</v>
+        <v>-15.34772624722759</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.96749853848551</v>
       </c>
       <c r="E11">
-        <v>-17.9683855526859</v>
+        <v>-22.65953742115154</v>
       </c>
       <c r="F11">
-        <v>2.294427624007216</v>
+        <v>2.112615889705975</v>
       </c>
       <c r="G11">
-        <v>-13.78578041623469</v>
+        <v>-14.90063493062714</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.33894746163708</v>
       </c>
       <c r="E12">
-        <v>-18.67555699817578</v>
+        <v>-21.88596027978897</v>
       </c>
       <c r="F12">
-        <v>2.862473943537755</v>
+        <v>2.417683723339366</v>
       </c>
       <c r="G12">
-        <v>-13.63169688121178</v>
+        <v>-13.82832119397459</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.799236447030578</v>
       </c>
       <c r="E13">
-        <v>-19.47490481580891</v>
+        <v>-22.51122624474191</v>
       </c>
       <c r="F13">
-        <v>2.342925221971516</v>
+        <v>2.186289229776158</v>
       </c>
       <c r="G13">
-        <v>-12.2215436568631</v>
+        <v>-13.88912543550162</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.392280433628508</v>
       </c>
       <c r="E14">
-        <v>-20.57769040604533</v>
+        <v>-23.68802206078678</v>
       </c>
       <c r="F14">
-        <v>3.555154765758701</v>
+        <v>2.951858099769432</v>
       </c>
       <c r="G14">
-        <v>-11.48902224486083</v>
+        <v>-12.48366763530006</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.12852125477819</v>
       </c>
       <c r="E15">
-        <v>-19.95166855663128</v>
+        <v>-23.63773497806575</v>
       </c>
       <c r="F15">
-        <v>3.29197415821527</v>
+        <v>2.887044977439594</v>
       </c>
       <c r="G15">
-        <v>-11.759075054621</v>
+        <v>-11.45720771127352</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.018468580266127</v>
       </c>
       <c r="E16">
-        <v>-21.31583234838446</v>
+        <v>-24.41410723064993</v>
       </c>
       <c r="F16">
-        <v>3.424282656525213</v>
+        <v>2.883598969043948</v>
       </c>
       <c r="G16">
-        <v>-10.49850574699245</v>
+        <v>-11.27962878030288</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.061820107984747</v>
       </c>
       <c r="E17">
-        <v>-22.10563608639313</v>
+        <v>-24.12145534785721</v>
       </c>
       <c r="F17">
-        <v>3.040826415564905</v>
+        <v>2.684588670725783</v>
       </c>
       <c r="G17">
-        <v>-9.493326002128081</v>
+        <v>-10.73097819373584</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.243128559268073</v>
       </c>
       <c r="E18">
-        <v>-22.48572137399614</v>
+        <v>-26.08775587069536</v>
       </c>
       <c r="F18">
-        <v>3.640276143335573</v>
+        <v>3.116444762296861</v>
       </c>
       <c r="G18">
-        <v>-9.571405540614506</v>
+        <v>-10.35873300844572</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.55908824370002</v>
       </c>
       <c r="E19">
-        <v>-24.30256858731033</v>
+        <v>-26.03203223435013</v>
       </c>
       <c r="F19">
-        <v>3.753881762425108</v>
+        <v>3.19461779409905</v>
       </c>
       <c r="G19">
-        <v>-8.667372568071343</v>
+        <v>-10.29026231542689</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.987188553359114</v>
       </c>
       <c r="E20">
-        <v>-23.39630465054215</v>
+        <v>-27.0000668831525</v>
       </c>
       <c r="F20">
-        <v>4.658859896105123</v>
+        <v>2.77326540119547</v>
       </c>
       <c r="G20">
-        <v>-8.096330930518613</v>
+        <v>-10.06635572168694</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.524513808492655</v>
       </c>
       <c r="E21">
-        <v>-22.47162537475967</v>
+        <v>-27.44093026528304</v>
       </c>
       <c r="F21">
-        <v>3.930597380464327</v>
+        <v>3.137044602869679</v>
       </c>
       <c r="G21">
-        <v>-7.955857207049171</v>
+        <v>-9.434298372295304</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.151800101861225</v>
       </c>
       <c r="E22">
-        <v>-23.36359811135912</v>
+        <v>-28.45484959280211</v>
       </c>
       <c r="F22">
-        <v>4.043576753797346</v>
+        <v>3.215007229351557</v>
       </c>
       <c r="G22">
-        <v>-6.841355143176525</v>
+        <v>-8.898379081726821</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.8632841383676773</v>
       </c>
       <c r="E23">
-        <v>-24.38381786045795</v>
+        <v>-28.66552746707103</v>
       </c>
       <c r="F23">
-        <v>3.976016765159823</v>
+        <v>3.066716210372001</v>
       </c>
       <c r="G23">
-        <v>-7.638073459301975</v>
+        <v>-8.784635466753492</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.6532775472605501</v>
       </c>
       <c r="E24">
-        <v>-24.91662503489756</v>
+        <v>-28.78144982496398</v>
       </c>
       <c r="F24">
-        <v>4.67119760020242</v>
+        <v>3.75434399143587</v>
       </c>
       <c r="G24">
-        <v>-7.700437620722194</v>
+        <v>-8.674558642558383</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.5180555230555075</v>
       </c>
       <c r="E25">
-        <v>-26.66628990182132</v>
+        <v>-28.42951500372066</v>
       </c>
       <c r="F25">
-        <v>4.300498217245224</v>
+        <v>3.458948175597567</v>
       </c>
       <c r="G25">
-        <v>-8.78854636215098</v>
+        <v>-9.065231768544871</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.4603962890921027</v>
       </c>
       <c r="E26">
-        <v>-24.38613535237721</v>
+        <v>-28.43848594018229</v>
       </c>
       <c r="F26">
-        <v>3.920448223045227</v>
+        <v>3.46158569740808</v>
       </c>
       <c r="G26">
-        <v>-8.576732737357073</v>
+        <v>-8.56414503231102</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.4744367834336493</v>
       </c>
       <c r="E27">
-        <v>-25.67140889501527</v>
+        <v>-28.56151651925768</v>
       </c>
       <c r="F27">
-        <v>3.816274395203967</v>
+        <v>3.586765265849531</v>
       </c>
       <c r="G27">
-        <v>-7.168755568625087</v>
+        <v>-9.467725040667624</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.5575150575015685</v>
       </c>
       <c r="E28">
-        <v>-25.12233774502764</v>
+        <v>-28.79417941767458</v>
       </c>
       <c r="F28">
-        <v>4.234732472402166</v>
+        <v>3.375089229942561</v>
       </c>
       <c r="G28">
-        <v>-8.074959375295759</v>
+        <v>-9.33375598734694</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.6960931801332202</v>
       </c>
       <c r="E29">
-        <v>-25.41171274408507</v>
+        <v>-29.24088844474482</v>
       </c>
       <c r="F29">
-        <v>3.894475591497851</v>
+        <v>3.52662082220187</v>
       </c>
       <c r="G29">
-        <v>-7.948643719743925</v>
+        <v>-9.103637126852442</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.87704085550747</v>
       </c>
       <c r="E30">
-        <v>-26.02630080272187</v>
+        <v>-28.3022336128543</v>
       </c>
       <c r="F30">
-        <v>4.77932771075945</v>
+        <v>3.53839192299565</v>
       </c>
       <c r="G30">
-        <v>-8.117904818447277</v>
+        <v>-8.965379925540857</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.085165519569729</v>
       </c>
       <c r="E31">
-        <v>-25.12232943860499</v>
+        <v>-28.08439560226138</v>
       </c>
       <c r="F31">
-        <v>4.202596787377961</v>
+        <v>3.739329003892727</v>
       </c>
       <c r="G31">
-        <v>-8.487528816167913</v>
+        <v>-9.650905324158495</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.304050604989758</v>
       </c>
       <c r="E32">
-        <v>-25.24564243605047</v>
+        <v>-28.50041862745813</v>
       </c>
       <c r="F32">
-        <v>4.398487454057182</v>
+        <v>3.930657022917329</v>
       </c>
       <c r="G32">
-        <v>-9.031472230237185</v>
+        <v>-10.00126202679672</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.523268849550001</v>
       </c>
       <c r="E33">
-        <v>-25.58437419849216</v>
+        <v>-27.82016829777579</v>
       </c>
       <c r="F33">
-        <v>4.170169517027972</v>
+        <v>3.777067766029466</v>
       </c>
       <c r="G33">
-        <v>-8.338379588422203</v>
+        <v>-9.190273380736242</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.731568295725412</v>
       </c>
       <c r="E34">
-        <v>-23.56980920684818</v>
+        <v>-27.49145823426091</v>
       </c>
       <c r="F34">
-        <v>4.814846448256687</v>
+        <v>4.006422819046982</v>
       </c>
       <c r="G34">
-        <v>-8.921770047890901</v>
+        <v>-9.014810458256699</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.92458703105134</v>
       </c>
       <c r="E35">
-        <v>-23.89250957357604</v>
+        <v>-27.30474646594192</v>
       </c>
       <c r="F35">
-        <v>4.520363493296268</v>
+        <v>4.186658998548099</v>
       </c>
       <c r="G35">
-        <v>-9.702295220689971</v>
+        <v>-10.01940148021577</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.098568838995329</v>
       </c>
       <c r="E36">
-        <v>-22.88523953738802</v>
+        <v>-26.92405065627416</v>
       </c>
       <c r="F36">
-        <v>4.947315649842773</v>
+        <v>4.174356085881721</v>
       </c>
       <c r="G36">
-        <v>-8.270313560814992</v>
+        <v>-10.49244751416877</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.253472722000301</v>
       </c>
       <c r="E37">
-        <v>-22.72883790531763</v>
+        <v>-25.9280648952557</v>
       </c>
       <c r="F37">
-        <v>4.689779537782018</v>
+        <v>4.402864547413575</v>
       </c>
       <c r="G37">
-        <v>-9.211090152733483</v>
+        <v>-9.811069283334113</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.390274293921034</v>
       </c>
       <c r="E38">
-        <v>-21.24204224277623</v>
+        <v>-26.60355979797111</v>
       </c>
       <c r="F38">
-        <v>4.341093190186816</v>
+        <v>4.026678058780236</v>
       </c>
       <c r="G38">
-        <v>-9.34084546428411</v>
+        <v>-9.759326936282839</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.508300758258742</v>
       </c>
       <c r="E39">
-        <v>-21.35872671494729</v>
+        <v>-24.45073855453492</v>
       </c>
       <c r="F39">
-        <v>5.039145146647515</v>
+        <v>4.689890539013993</v>
       </c>
       <c r="G39">
-        <v>-9.887250810502799</v>
+        <v>-10.07082270568234</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.609215709619564</v>
       </c>
       <c r="E40">
-        <v>-20.74670534090923</v>
+        <v>-25.23820818777903</v>
       </c>
       <c r="F40">
-        <v>5.093373390304381</v>
+        <v>4.184382644925206</v>
       </c>
       <c r="G40">
-        <v>-8.836499213428253</v>
+        <v>-10.12287050985077</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.69019306537002</v>
       </c>
       <c r="E41">
-        <v>-20.18852619848625</v>
+        <v>-24.493508324758</v>
       </c>
       <c r="F41">
-        <v>4.759289503285729</v>
+        <v>3.925549309511667</v>
       </c>
       <c r="G41">
-        <v>-9.559544927937077</v>
+        <v>-10.20881622179022</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.751487273555904</v>
       </c>
       <c r="E42">
-        <v>-20.07130180884296</v>
+        <v>-24.09331318792017</v>
       </c>
       <c r="F42">
-        <v>5.614678250764555</v>
+        <v>4.148178019218451</v>
       </c>
       <c r="G42">
-        <v>-9.000266000139607</v>
+        <v>-10.7328696781921</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.789331038099421</v>
       </c>
       <c r="E43">
-        <v>-20.47407608991351</v>
+        <v>-23.81912648267764</v>
       </c>
       <c r="F43">
-        <v>4.754100609874594</v>
+        <v>4.526014615718166</v>
       </c>
       <c r="G43">
-        <v>-9.873949066811077</v>
+        <v>-10.64501159583966</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.802800731050056</v>
       </c>
       <c r="E44">
-        <v>-18.97716735779616</v>
+        <v>-22.8310899681349</v>
       </c>
       <c r="F44">
-        <v>4.785999381821597</v>
+        <v>4.388732599521815</v>
       </c>
       <c r="G44">
-        <v>-9.65283988590051</v>
+        <v>-10.38600876256138</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.790589176421402</v>
       </c>
       <c r="E45">
-        <v>-20.02943328547737</v>
+        <v>-21.98626033328358</v>
       </c>
       <c r="F45">
-        <v>4.872517386839589</v>
+        <v>4.527992757076052</v>
       </c>
       <c r="G45">
-        <v>-10.22147311156794</v>
+        <v>-10.38990268811902</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.753489096009016</v>
       </c>
       <c r="E46">
-        <v>-19.82621250214218</v>
+        <v>-22.37019149457338</v>
       </c>
       <c r="F46">
-        <v>5.183566033121192</v>
+        <v>4.367556215236649</v>
       </c>
       <c r="G46">
-        <v>-10.98622024943062</v>
+        <v>-10.75570455575827</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.696223323605239</v>
       </c>
       <c r="E47">
-        <v>-18.13659476455278</v>
+        <v>-23.11774876698589</v>
       </c>
       <c r="F47">
-        <v>4.885348797908953</v>
+        <v>4.421289095186642</v>
       </c>
       <c r="G47">
-        <v>-9.386681001697989</v>
+        <v>-11.04799307720095</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.623013316068278</v>
       </c>
       <c r="E48">
-        <v>-17.48661303900579</v>
+        <v>-21.65593051735202</v>
       </c>
       <c r="F48">
-        <v>4.617751335373795</v>
+        <v>4.710409199581337</v>
       </c>
       <c r="G48">
-        <v>-10.08864495363357</v>
+        <v>-10.94477859516358</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.545633798874457</v>
       </c>
       <c r="E49">
-        <v>-16.50696185812788</v>
+        <v>-21.76431272008474</v>
       </c>
       <c r="F49">
-        <v>4.442535062333643</v>
+        <v>4.629537346780826</v>
       </c>
       <c r="G49">
-        <v>-9.660672119673851</v>
+        <v>-10.87960266181873</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.472158549824343</v>
       </c>
       <c r="E50">
-        <v>-17.1781914128127</v>
+        <v>-21.93461515045934</v>
       </c>
       <c r="F50">
-        <v>4.61697764021958</v>
+        <v>4.515842264011789</v>
       </c>
       <c r="G50">
-        <v>-10.2545943228231</v>
+        <v>-10.77257127118916</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.417730843149659</v>
       </c>
       <c r="E51">
-        <v>-16.89300700398202</v>
+        <v>-20.75146492108748</v>
       </c>
       <c r="F51">
-        <v>4.618216877854168</v>
+        <v>4.267567299514332</v>
       </c>
       <c r="G51">
-        <v>-10.80028040890694</v>
+        <v>-10.94544564040661</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.392375193740115</v>
       </c>
       <c r="E52">
-        <v>-17.77418969755957</v>
+        <v>-21.51542737823307</v>
       </c>
       <c r="F52">
-        <v>4.925095522630079</v>
+        <v>4.062201766481889</v>
       </c>
       <c r="G52">
-        <v>-11.1260948070164</v>
+        <v>-10.88717904262214</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.408699159878306</v>
       </c>
       <c r="E53">
-        <v>-18.42280916979202</v>
+        <v>-19.39419961334484</v>
       </c>
       <c r="F53">
-        <v>4.510452905689175</v>
+        <v>4.689943554527772</v>
       </c>
       <c r="G53">
-        <v>-10.32816902151756</v>
+        <v>-11.06697580112293</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.477256838628787</v>
       </c>
       <c r="E54">
-        <v>-15.21388027819914</v>
+        <v>-19.12418273227244</v>
       </c>
       <c r="F54">
-        <v>4.864586597325186</v>
+        <v>4.067804843594426</v>
       </c>
       <c r="G54">
-        <v>-9.534951713888791</v>
+        <v>-11.1517988928882</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.601209512613598</v>
       </c>
       <c r="E55">
-        <v>-16.93401996581471</v>
+        <v>-19.77168499065851</v>
       </c>
       <c r="F55">
-        <v>5.361628576557362</v>
+        <v>3.906659219258227</v>
       </c>
       <c r="G55">
-        <v>-10.56193378683355</v>
+        <v>-10.83103759093484</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.786969383833223</v>
       </c>
       <c r="E56">
-        <v>-15.3837424681733</v>
+        <v>-19.56635022275898</v>
       </c>
       <c r="F56">
-        <v>4.634201055258588</v>
+        <v>3.940733284004982</v>
       </c>
       <c r="G56">
-        <v>-11.72770173686959</v>
+        <v>-11.63648362622838</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.027258793937112</v>
       </c>
       <c r="E57">
-        <v>-15.36562200716308</v>
+        <v>-18.66588001578893</v>
       </c>
       <c r="F57">
-        <v>5.166703786269805</v>
+        <v>4.320231585514714</v>
       </c>
       <c r="G57">
-        <v>-11.11624968916331</v>
+        <v>-11.90477418338955</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.320510934783557</v>
       </c>
       <c r="E58">
-        <v>-14.69620740582721</v>
+        <v>-18.11499391245235</v>
       </c>
       <c r="F58">
-        <v>3.764764853363088</v>
+        <v>4.322052337066067</v>
       </c>
       <c r="G58">
-        <v>-10.66977972977555</v>
+        <v>-11.70937822595686</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.653975103877214</v>
       </c>
       <c r="E59">
-        <v>-14.62465172791174</v>
+        <v>-18.54704002694029</v>
       </c>
       <c r="F59">
-        <v>3.939822079861902</v>
+        <v>3.841163522188481</v>
       </c>
       <c r="G59">
-        <v>-11.76017678883845</v>
+        <v>-12.49392786154313</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.01963441833076</v>
       </c>
       <c r="E60">
-        <v>-13.8034372526534</v>
+        <v>-17.85835867826854</v>
       </c>
       <c r="F60">
-        <v>3.866912494537101</v>
+        <v>4.113484335654402</v>
       </c>
       <c r="G60">
-        <v>-11.93706387249244</v>
+        <v>-11.98031477276112</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.40753008942164</v>
       </c>
       <c r="E61">
-        <v>-13.95826066442035</v>
+        <v>-17.6051290773711</v>
       </c>
       <c r="F61">
-        <v>4.408625014332643</v>
+        <v>4.011348291624028</v>
       </c>
       <c r="G61">
-        <v>-12.08010787401183</v>
+        <v>-12.34234933595539</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.806453221995231</v>
       </c>
       <c r="E62">
-        <v>-13.18176381549643</v>
+        <v>-17.06410685093098</v>
       </c>
       <c r="F62">
-        <v>5.337074110003579</v>
+        <v>4.000052673719454</v>
       </c>
       <c r="G62">
-        <v>-11.45192225884881</v>
+        <v>-12.62873626924986</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.214494468527473</v>
       </c>
       <c r="E63">
-        <v>-13.64944863636273</v>
+        <v>-16.90920868136018</v>
       </c>
       <c r="F63">
-        <v>4.028788738922569</v>
+        <v>3.919868365863268</v>
       </c>
       <c r="G63">
-        <v>-11.98331321292401</v>
+        <v>-13.6334813251398</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.620458525833512</v>
       </c>
       <c r="E64">
-        <v>-13.1232782936202</v>
+        <v>-16.71164041863808</v>
       </c>
       <c r="F64">
-        <v>3.985665588667632</v>
+        <v>3.985483347839017</v>
       </c>
       <c r="G64">
-        <v>-12.00076995663249</v>
+        <v>-12.88021885273344</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.026600516394883</v>
       </c>
       <c r="E65">
-        <v>-14.40064412189579</v>
+        <v>-17.1121844252272</v>
       </c>
       <c r="F65">
-        <v>4.678483919877443</v>
+        <v>3.539213663459228</v>
       </c>
       <c r="G65">
-        <v>-12.63063689131219</v>
+        <v>-12.97077513962079</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.423829791219618</v>
       </c>
       <c r="E66">
-        <v>-12.8367856232222</v>
+        <v>-16.61794397114995</v>
       </c>
       <c r="F66">
-        <v>3.99818719032835</v>
+        <v>4.02898754709924</v>
       </c>
       <c r="G66">
-        <v>-13.27186448108011</v>
+        <v>-13.23283907093215</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.813124623498285</v>
       </c>
       <c r="E67">
-        <v>-11.95098871186277</v>
+        <v>-17.8048403971368</v>
       </c>
       <c r="F67">
-        <v>4.571515180419138</v>
+        <v>3.965531290575187</v>
       </c>
       <c r="G67">
-        <v>-11.29655684823166</v>
+        <v>-13.12455582827114</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.190075441038363</v>
       </c>
       <c r="E68">
-        <v>-14.37802157980945</v>
+        <v>-16.74538941386364</v>
       </c>
       <c r="F68">
-        <v>5.030826681188602</v>
+        <v>3.951144205523366</v>
       </c>
       <c r="G68">
-        <v>-11.69551256143346</v>
+        <v>-13.30424032475451</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.552884542127368</v>
       </c>
       <c r="E69">
-        <v>-11.28567333010451</v>
+        <v>-17.23871616144942</v>
       </c>
       <c r="F69">
-        <v>3.827177366959614</v>
+        <v>3.731913458902866</v>
       </c>
       <c r="G69">
-        <v>-12.30912630566118</v>
+        <v>-13.02050329722002</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.905351841058336</v>
       </c>
       <c r="E70">
-        <v>-15.41567235683859</v>
+        <v>-16.89366321137134</v>
       </c>
       <c r="F70">
-        <v>4.502697730064166</v>
+        <v>3.873731614996947</v>
       </c>
       <c r="G70">
-        <v>-13.00145922080014</v>
+        <v>-12.90848407904912</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.240708206129925</v>
       </c>
       <c r="E71">
-        <v>-12.05106449194584</v>
+        <v>-17.27678449645281</v>
       </c>
       <c r="F71">
-        <v>4.181589390042966</v>
+        <v>3.766305616732295</v>
       </c>
       <c r="G71">
-        <v>-13.15545268513467</v>
+        <v>-13.02799743956881</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.568269268168992</v>
       </c>
       <c r="E72">
-        <v>-13.29366794143261</v>
+        <v>-17.78930738678195</v>
       </c>
       <c r="F72">
-        <v>3.524833205346628</v>
+        <v>3.836705248826614</v>
       </c>
       <c r="G72">
-        <v>-11.39242600036193</v>
+        <v>-13.37246038629259</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.880929614322554</v>
       </c>
       <c r="E73">
-        <v>-12.49235150163152</v>
+        <v>-16.72586932063695</v>
       </c>
       <c r="F73">
-        <v>4.007638862394292</v>
+        <v>3.676485739246745</v>
       </c>
       <c r="G73">
-        <v>-13.28560874598003</v>
+        <v>-13.19571428284652</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.186576074099536</v>
       </c>
       <c r="E74">
-        <v>-14.77604458712439</v>
+        <v>-16.34480387516128</v>
       </c>
       <c r="F74">
-        <v>3.869323043679247</v>
+        <v>3.677113641738067</v>
       </c>
       <c r="G74">
-        <v>-13.59854825713841</v>
+        <v>-13.49287445369622</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.478782598413977</v>
       </c>
       <c r="E75">
-        <v>-12.07197175775503</v>
+        <v>-16.84522430768987</v>
       </c>
       <c r="F75">
-        <v>4.012814501926983</v>
+        <v>3.848497887172868</v>
       </c>
       <c r="G75">
-        <v>-11.94779403276192</v>
+        <v>-13.08598207693744</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.759780353597966</v>
       </c>
       <c r="E76">
-        <v>-16.13191441586189</v>
+        <v>-18.02173770536465</v>
       </c>
       <c r="F76">
-        <v>5.213002897147075</v>
+        <v>3.882977851946995</v>
       </c>
       <c r="G76">
-        <v>-11.98552451359268</v>
+        <v>-12.60867791855633</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.02788579730156</v>
       </c>
       <c r="E77">
-        <v>-14.73956693205842</v>
+        <v>-18.6085158609704</v>
       </c>
       <c r="F77">
-        <v>4.430777215418307</v>
+        <v>3.279368063079467</v>
       </c>
       <c r="G77">
-        <v>-11.15247246499271</v>
+        <v>-12.76347940834181</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.2755374653511</v>
       </c>
       <c r="E78">
-        <v>-15.74853147846697</v>
+        <v>-18.56839583957256</v>
       </c>
       <c r="F78">
-        <v>3.607500958676408</v>
+        <v>3.602487679154665</v>
       </c>
       <c r="G78">
-        <v>-12.07602075335445</v>
+        <v>-13.18509638459446</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.50492226602226</v>
       </c>
       <c r="E79">
-        <v>-15.41847992769417</v>
+        <v>-19.10129023144998</v>
       </c>
       <c r="F79">
-        <v>3.703571696583483</v>
+        <v>3.520558829548183</v>
       </c>
       <c r="G79">
-        <v>-11.26915055688645</v>
+        <v>-12.35048702684589</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.7002317318135</v>
       </c>
       <c r="E80">
-        <v>-16.51923044438143</v>
+        <v>-19.16324783799378</v>
       </c>
       <c r="F80">
-        <v>4.594507346051241</v>
+        <v>3.579016717163744</v>
       </c>
       <c r="G80">
-        <v>-11.33671532153217</v>
+        <v>-12.38576079701642</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.85923848587722</v>
       </c>
       <c r="E81">
-        <v>-15.87687401482682</v>
+        <v>-20.26379069411479</v>
       </c>
       <c r="F81">
-        <v>3.176049110397897</v>
+        <v>3.538302459316148</v>
       </c>
       <c r="G81">
-        <v>-12.08444823689456</v>
+        <v>-12.19764620624834</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.96043450761391</v>
       </c>
       <c r="E82">
-        <v>-17.88908413564963</v>
+        <v>-21.25079721224897</v>
       </c>
       <c r="F82">
-        <v>4.136448336794809</v>
+        <v>3.446095226975729</v>
       </c>
       <c r="G82">
-        <v>-11.29144239957767</v>
+        <v>-11.72685977173895</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.99579173559406</v>
       </c>
       <c r="E83">
-        <v>-15.84635621801198</v>
+        <v>-21.63923876103753</v>
       </c>
       <c r="F83">
-        <v>3.97315724088536</v>
+        <v>3.831349025200113</v>
       </c>
       <c r="G83">
-        <v>-11.25405392628834</v>
+        <v>-11.45474969524099</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.94668707130534</v>
       </c>
       <c r="E84">
-        <v>-20.04284815805656</v>
+        <v>-22.89901573935247</v>
       </c>
       <c r="F84">
-        <v>3.545684869609897</v>
+        <v>3.563025912820102</v>
       </c>
       <c r="G84">
-        <v>-11.33079415279952</v>
+        <v>-11.7044008413939</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.80272430269046</v>
       </c>
       <c r="E85">
-        <v>-19.04188684987096</v>
+        <v>-22.54755438420018</v>
       </c>
       <c r="F85">
-        <v>3.370614389232639</v>
+        <v>3.542754105738793</v>
       </c>
       <c r="G85">
-        <v>-9.982640891000601</v>
+        <v>-11.73023676986756</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-10.5573988553223</v>
       </c>
       <c r="E86">
-        <v>-21.20880824575495</v>
+        <v>-24.04001087377732</v>
       </c>
       <c r="F86">
-        <v>4.29202567544939</v>
+        <v>3.551728638180723</v>
       </c>
       <c r="G86">
-        <v>-9.718643703319522</v>
+        <v>-11.33063489737946</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-10.20313844300209</v>
       </c>
       <c r="E87">
-        <v>-21.63787650772299</v>
+        <v>-25.04018722502253</v>
       </c>
       <c r="F87">
-        <v>3.459962097298593</v>
+        <v>3.323602882388961</v>
       </c>
       <c r="G87">
-        <v>-10.04820713066182</v>
+        <v>-11.73317255216027</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.748973732285725</v>
       </c>
       <c r="E88">
-        <v>-21.71101871236455</v>
+        <v>-25.00325271671083</v>
       </c>
       <c r="F88">
-        <v>4.305582736363607</v>
+        <v>3.604149384164681</v>
       </c>
       <c r="G88">
-        <v>-9.723354791934186</v>
+        <v>-10.85234257217062</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.197993354234153</v>
       </c>
       <c r="E89">
-        <v>-23.87606285672971</v>
+        <v>-27.56466689028366</v>
       </c>
       <c r="F89">
-        <v>3.163817437328159</v>
+        <v>3.471612256451566</v>
       </c>
       <c r="G89">
-        <v>-9.307211241716796</v>
+        <v>-11.16166750744261</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.573713561372656</v>
       </c>
       <c r="E90">
-        <v>-27.47879924614283</v>
+        <v>-28.18070441967283</v>
       </c>
       <c r="F90">
-        <v>3.885259175774304</v>
+        <v>3.839218515526708</v>
       </c>
       <c r="G90">
-        <v>-9.623449428666053</v>
+        <v>-10.4885601154726</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.888730798043296</v>
       </c>
       <c r="E91">
-        <v>-27.07168901244916</v>
+        <v>-30.14008153923249</v>
       </c>
       <c r="F91">
-        <v>3.736731243717547</v>
+        <v>3.310234689242582</v>
       </c>
       <c r="G91">
-        <v>-9.616653660495386</v>
+        <v>-10.32768472839591</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.171241651588415</v>
       </c>
       <c r="E92">
-        <v>-28.13869053391086</v>
+        <v>-31.38156985147855</v>
       </c>
       <c r="F92">
-        <v>3.503095187962364</v>
+        <v>3.302923518545474</v>
       </c>
       <c r="G92">
-        <v>-9.750997355664893</v>
+        <v>-9.833983788610315</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.43996354658465</v>
       </c>
       <c r="E93">
-        <v>-29.12243262794373</v>
+        <v>-32.80236267964577</v>
       </c>
       <c r="F93">
-        <v>3.636901374536567</v>
+        <v>2.871257951477041</v>
       </c>
       <c r="G93">
-        <v>-9.713678067107224</v>
+        <v>-9.988921037114524</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.713884190276403</v>
       </c>
       <c r="E94">
-        <v>-31.01950742441963</v>
+        <v>-33.60601945402841</v>
       </c>
       <c r="F94">
-        <v>3.568112088673291</v>
+        <v>3.191175099173015</v>
       </c>
       <c r="G94">
-        <v>-9.79859645105007</v>
+        <v>-9.565379942098216</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.010960165024069</v>
       </c>
       <c r="E95">
-        <v>-35.29615011321642</v>
+        <v>-36.19413046999723</v>
       </c>
       <c r="F95">
-        <v>3.992307438503279</v>
+        <v>3.275103627689856</v>
       </c>
       <c r="G95">
-        <v>-9.422740605990446</v>
+        <v>-9.816805089200789</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.334269648629586</v>
       </c>
       <c r="E96">
-        <v>-38.56773850406698</v>
+        <v>-38.85387192168538</v>
       </c>
       <c r="F96">
-        <v>2.871281145764319</v>
+        <v>2.928660499021435</v>
       </c>
       <c r="G96">
-        <v>-9.05927404938795</v>
+        <v>-9.835654665148628</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.696149885921147</v>
       </c>
       <c r="E97">
-        <v>-37.21581837929939</v>
+        <v>-40.4532486836089</v>
       </c>
       <c r="F97">
-        <v>2.647095105340272</v>
+        <v>2.407756568384217</v>
       </c>
       <c r="G97">
-        <v>-8.173111623570959</v>
+        <v>-9.560456077799376</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.082040701953466</v>
       </c>
       <c r="E98">
-        <v>-39.76639059470876</v>
+        <v>-42.05765083123547</v>
       </c>
       <c r="F98">
-        <v>3.121950092055866</v>
+        <v>2.220285427987049</v>
       </c>
       <c r="G98">
-        <v>-8.745697516549333</v>
+        <v>-8.586930305729961</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.504076176191353</v>
       </c>
       <c r="E99">
-        <v>-43.95578884981053</v>
+        <v>-43.63811594539138</v>
       </c>
       <c r="F99">
-        <v>2.27078933180093</v>
+        <v>1.955839075052141</v>
       </c>
       <c r="G99">
-        <v>-9.227796307372017</v>
+        <v>-9.065853125757556</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-1.938670811216382</v>
       </c>
       <c r="E100">
-        <v>-44.59476664195239</v>
+        <v>-46.42772416199559</v>
       </c>
       <c r="F100">
-        <v>2.43121924670111</v>
+        <v>1.788706011128507</v>
       </c>
       <c r="G100">
-        <v>-9.084985967493528</v>
+        <v>-9.481631171732188</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.410427499916211</v>
       </c>
       <c r="E101">
-        <v>-47.8253431092731</v>
+        <v>-48.08933160410751</v>
       </c>
       <c r="F101">
-        <v>2.603347366063625</v>
+        <v>1.255838798460058</v>
       </c>
       <c r="G101">
-        <v>-8.974212074492593</v>
+        <v>-9.405111553138953</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.8807513202469016</v>
       </c>
       <c r="E102">
-        <v>-47.64151055470505</v>
+        <v>-49.77356262660861</v>
       </c>
       <c r="F102">
-        <v>1.912710954592787</v>
+        <v>1.136497563473538</v>
       </c>
       <c r="G102">
-        <v>-9.39916688770499</v>
+        <v>-8.572321884370387</v>
       </c>
     </row>
   </sheetData>
